--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487960_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487960_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. PEREZ CABELLO</t>
+          <t>D. BUSTO VERANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4929</v>
+        <v>0.5582</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4317</v>
+        <v>-0.3676</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9246</v>
+        <v>0.9258</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7881</v>
+        <v>-1.7547</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3656</v>
+        <v>-3.1457</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.1537</v>
+        <v>1.3909</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2152</v>
+        <v>-1.2499</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4237</v>
+        <v>-3.0255</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.639</v>
+        <v>1.7756</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5729</v>
+        <v>-0.5048</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0581</v>
+        <v>-0.1201</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5148</v>
+        <v>-0.3847</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3964</v>
+        <v>-0.5947</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6864</v>
+        <v>0.9076</v>
       </c>
       <c r="T2" t="n">
-        <v>0.18</v>
+        <v>0.2699</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5064</v>
+        <v>0.6377</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. BUSTO VERANO</t>
+          <t>J. PEREZ CABELLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4387</v>
+        <v>0.3764</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5713</v>
+        <v>-0.2674</v>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>0.6438</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.7547</v>
+        <v>-0.7881</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.1457</v>
+        <v>0.3656</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3909</v>
+        <v>-1.1537</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.2499</v>
+        <v>-0.2152</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.0255</v>
+        <v>0.4237</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7756</v>
+        <v>-0.639</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5048</v>
+        <v>-0.5729</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1201</v>
+        <v>-0.0581</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3847</v>
+        <v>-0.5148</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1982</v>
+        <v>0.5947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7881</v>
+        <v>0.5698</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.3442</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7219</v>
+        <v>0.2256</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TORIL RAYO</t>
+          <t>R. ALMAGRO LAZARO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,55 +721,55 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.2976</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7551</v>
+        <v>0.2856</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8319</v>
+        <v>0.012</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5558</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7357</v>
+        <v>0.5487</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1799</v>
+        <v>-0.486</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.9885</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0133</v>
+        <v>0.9484</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0804</v>
+        <v>0.0402</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4888</v>
+        <v>-0.9258</v>
       </c>
       <c r="N4" t="n">
-        <v>0.749</v>
+        <v>-0.3996</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2602</v>
+        <v>-0.5262</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1893</v>
+        <v>-0.5947</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5121</v>
+        <v>0.0367</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3671</v>
+        <v>-0.1082</v>
       </c>
       <c r="U4" t="n">
         <v>0.145</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. ALMAGRO LAZARO</t>
+          <t>A. TORIL RAYO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0746</v>
+        <v>0.0135</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0819</v>
+        <v>-0.9588</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1564</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.5558</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5487</v>
+        <v>0.7357</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.486</v>
+        <v>-0.1799</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9885</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9484</v>
+        <v>-0.0133</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0402</v>
+        <v>0.0804</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9258</v>
+        <v>0.4888</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3996</v>
+        <v>0.749</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5262</v>
+        <v>-0.2602</v>
       </c>
       <c r="P5" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1.1893</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.1982</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-0.5947</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.7929</v>
-      </c>
       <c r="S5" t="n">
-        <v>-0.3355</v>
+        <v>0.4488</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.312</v>
+        <v>0.1634</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0235</v>
+        <v>0.2854</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ESPINAL REYNOSO</t>
+          <t>F. DAYER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0182</v>
+        <v>-0.7423</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1089</v>
+        <v>0.4568</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0907</v>
+        <v>-1.199</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.426</v>
+        <v>-1.9215</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6767</v>
+        <v>-1.4031</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1027</v>
+        <v>-0.5184</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0734</v>
+        <v>0.7782</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0656</v>
+        <v>-0.2819</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0078</v>
+        <v>1.0602</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.4994</v>
+        <v>-2.6998</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3889</v>
+        <v>-1.1212</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1105</v>
+        <v>-1.5786</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.784</v>
+        <v>-3.568</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.3609</v>
+        <v>-5.1538</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5769</v>
+        <v>1.5858</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1214</v>
+        <v>0.0596</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1787</v>
+        <v>-0.1219</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9428</v>
+        <v>0.1815</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0704</v>
+        <v>4.6876</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>4.9542</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0704</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4584</v>
+        <v>-1.0031</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6838</v>
+        <v>-1.9478</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2255</v>
+        <v>0.9447</v>
       </c>
       <c r="G7" t="n">
         <v>-2.6603</v>
@@ -1000,13 +1000,13 @@
         <v>1.784</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2827</v>
+        <v>0.1725</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2259</v>
+        <v>-0.4899</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9432</v>
+        <v>0.6624</v>
       </c>
       <c r="V7" t="n">
         <v>1.8811</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. DAYER</t>
+          <t>J. MORALES MUNOZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0148</v>
+        <v>-1.0577</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6472</v>
+        <v>-1.4231</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3675</v>
+        <v>0.3655</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9215</v>
+        <v>-1.5001</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4031</v>
+        <v>-0.624</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5184</v>
+        <v>-0.8761</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7782</v>
+        <v>-0.3258</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2819</v>
+        <v>-0.1003</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0602</v>
+        <v>-0.2255</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6998</v>
+        <v>-1.1743</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1212</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5786</v>
+        <v>-0.6506</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.568</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.1538</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5858</v>
+        <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2129</v>
+        <v>0.5635</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2259</v>
+        <v>0.0148</v>
       </c>
       <c r="U8" t="n">
-        <v>0.013</v>
+        <v>0.5486</v>
       </c>
       <c r="V8" t="n">
-        <v>4.6876</v>
+        <v>0.8701</v>
       </c>
       <c r="W8" t="n">
-        <v>4.9542</v>
+        <v>0.8701</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MORALES MUNOZ</t>
+          <t>J. ESPINAL REYNOSO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0411</v>
+        <v>-2.1586</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2381</v>
+        <v>-1.9404</v>
       </c>
       <c r="F9" t="n">
-        <v>0.197</v>
+        <v>-0.2182</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5001</v>
+        <v>-1.426</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.624</v>
+        <v>0.6767</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8761</v>
+        <v>-2.1027</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3258</v>
+        <v>2.0734</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1003</v>
+        <v>2.0656</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2255</v>
+        <v>0.0078</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1743</v>
+        <v>-3.4994</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-1.3889</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6506</v>
+        <v>-2.1105</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9911</v>
+        <v>-1.784</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9822</v>
+        <v>-4.3609</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9911</v>
+        <v>2.5769</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.42</v>
+        <v>0.981</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8001</v>
+        <v>0.3471</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3802</v>
+        <v>0.6339</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8701</v>
+        <v>0.0704</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4257</v>
+        <v>-2.1596</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6008</v>
+        <v>-2.3347</v>
       </c>
       <c r="F10" t="n">
         <v>0.1751</v>
@@ -1234,10 +1234,10 @@
         <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>-0</v>
+        <v>0.2661</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.312</v>
+        <v>-0.0459</v>
       </c>
       <c r="U10" t="n">
         <v>0.312</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. REYES ORTEGA</t>
+          <t>R. URBANO MORENO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8474</v>
+        <v>-2.2961</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9382</v>
+        <v>-1.871</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09089999999999999</v>
+        <v>-0.4251</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2838</v>
+        <v>-1.9998</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4956</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7883</v>
+        <v>-2.5618</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.973</v>
+        <v>-0.8273</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9769</v>
+        <v>0.4105</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0039</v>
+        <v>-1.2377</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3109</v>
+        <v>-1.1725</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4813</v>
+        <v>0.1515</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7922</v>
+        <v>-1.3241</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3787</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8329</v>
+        <v>-0.3469</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4134</v>
+        <v>-0.3697</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4195</v>
+        <v>0.0228</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2071</v>
+        <v>-0.9405</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. URBANO MORENO</t>
+          <t>J. REYES ORTEGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0978</v>
+        <v>-3.7818</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3638</v>
+        <v>-3.9569</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.734</v>
+        <v>0.1751</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9998</v>
+        <v>-2.2838</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5620000000000001</v>
+        <v>-1.4956</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.5618</v>
+        <v>-0.7883</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8273</v>
+        <v>-1.973</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4105</v>
+        <v>-1.9769</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2377</v>
+        <v>0.0039</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1725</v>
+        <v>-0.3109</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1515</v>
+        <v>0.4813</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3241</v>
+        <v>-0.7922</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.3787</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1486</v>
+        <v>0.8985</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8625</v>
+        <v>0.3947</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.286</v>
+        <v>0.5037</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9405</v>
+        <v>-1.2071</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1481</v>
+        <v>-5.2281</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8151</v>
+        <v>-4.8109</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3329</v>
+        <v>-0.4172</v>
       </c>
       <c r="G13" t="n">
         <v>-4.5214</v>
@@ -1468,13 +1468,13 @@
         <v>1.1893</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1663</v>
+        <v>0.0863</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1125</v>
+        <v>0.1167</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0538</v>
+        <v>-0.0304</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.1177</v>
+        <v>-17.1816</v>
       </c>
       <c r="E14" t="n">
-        <v>-20.0721</v>
+        <v>-19.1362</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9549</v>
+        <v>1.9548</v>
       </c>
       <c r="G14" t="n">
         <v>-20.4647</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.723699999999999</v>
+        <v>-5.7237</v>
       </c>
       <c r="I14" t="n">
         <v>-14.7412</v>
@@ -1537,7 +1537,7 @@
         <v>-11.8538</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.928799999999999</v>
+        <v>-7.9288</v>
       </c>
       <c r="Q14" t="n">
         <v>-21.8045</v>
@@ -1546,13 +1546,13 @@
         <v>13.8755</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7075</v>
+        <v>4.6435</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4204999999999999</v>
+        <v>0.5152</v>
       </c>
       <c r="U14" t="n">
-        <v>4.1283</v>
+        <v>4.1282</v>
       </c>
       <c r="V14" t="n">
         <v>6.5687</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.548400000000001</v>
+        <v>8.2018</v>
       </c>
       <c r="E15" t="n">
-        <v>7.0756</v>
+        <v>5.6494</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4727</v>
+        <v>2.5524</v>
       </c>
       <c r="G15" t="n">
         <v>4.9172</v>
@@ -1624,13 +1624,13 @@
         <v>2.1805</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1137</v>
+        <v>0.7672</v>
       </c>
       <c r="T15" t="n">
-        <v>1.865</v>
+        <v>0.4388</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2487</v>
+        <v>0.3284</v>
       </c>
       <c r="V15" t="n">
         <v>0.337</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. TRUJILLO MARIN</t>
+          <t>O. DIAZ GUILLEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4194</v>
+        <v>4.0668</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1695</v>
+        <v>1.1647</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2499</v>
+        <v>2.902</v>
       </c>
       <c r="G16" t="n">
-        <v>5.4647</v>
+        <v>3.4498</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5306</v>
+        <v>0.9282</v>
       </c>
       <c r="I16" t="n">
-        <v>4.9341</v>
+        <v>2.5216</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9488</v>
+        <v>2.1967</v>
       </c>
       <c r="K16" t="n">
-        <v>0.445</v>
+        <v>0.377</v>
       </c>
       <c r="L16" t="n">
-        <v>4.5038</v>
+        <v>1.8197</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5159</v>
+        <v>1.2531</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0856</v>
+        <v>0.5512</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4303</v>
+        <v>0.7019</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1805</v>
+        <v>1.5858</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7698</v>
+        <v>-0.1937</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7267</v>
+        <v>-0.2568</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0431</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4737</v>
+        <v>1.2071</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0704</v>
+        <v>1.2071</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. DIAZ GUILLEN</t>
+          <t>E. TRUJILLO MARIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2146</v>
+        <v>4.0469</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7573</v>
+        <v>2.5769</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4574</v>
+        <v>1.47</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4498</v>
+        <v>5.4647</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9282</v>
+        <v>0.5306</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5216</v>
+        <v>4.9341</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1967</v>
+        <v>4.9488</v>
       </c>
       <c r="K17" t="n">
-        <v>0.377</v>
+        <v>0.445</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8197</v>
+        <v>4.5038</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2531</v>
+        <v>0.5159</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5512</v>
+        <v>0.0856</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7019</v>
+        <v>0.4303</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0458</v>
+        <v>-0.1423</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6643</v>
+        <v>-0.3192</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3815</v>
+        <v>0.1769</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2071</v>
+        <v>-1.4737</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2071</v>
+        <v>-0.0704</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4033</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4001</v>
+        <v>2.4236</v>
       </c>
       <c r="E18" t="n">
         <v>-0.2612</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6613</v>
+        <v>2.6848</v>
       </c>
       <c r="G18" t="n">
         <v>2.0888</v>
@@ -1858,13 +1858,13 @@
         <v>1.784</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.431</v>
+        <v>-0.4075</v>
       </c>
       <c r="T18" t="n">
         <v>-0.7488</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3178</v>
+        <v>0.3413</v>
       </c>
       <c r="V18" t="n">
         <v>0.9405</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2763</v>
+        <v>1.7852</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6197</v>
+        <v>-1.2144</v>
       </c>
       <c r="F19" t="n">
-        <v>4.896</v>
+        <v>2.9996</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0519</v>
+        <v>1.7159</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8243</v>
+        <v>1.1516</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2276</v>
+        <v>0.5643</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0034</v>
+        <v>1.0756</v>
       </c>
       <c r="K19" t="n">
-        <v>0.471</v>
+        <v>0.7944</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4744</v>
+        <v>0.2812</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0552</v>
+        <v>0.6403</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3533</v>
+        <v>0.3572</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7019</v>
+        <v>0.2831</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9822</v>
+        <v>2.3787</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5614</v>
+        <v>-0.5937</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2972</v>
+        <v>-0.5743</v>
       </c>
       <c r="U19" t="n">
-        <v>1.8585</v>
+        <v>-0.0194</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.337</v>
+        <v>0.2666</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.337</v>
+        <v>0.2666</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.24</v>
+        <v>1.7578</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0106</v>
+        <v>0.2776</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2506</v>
+        <v>1.4802</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7159</v>
+        <v>1.8957</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1516</v>
+        <v>-1.7145</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5643</v>
+        <v>3.6103</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0756</v>
+        <v>0.6427</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7944</v>
+        <v>-2.2657</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2812</v>
+        <v>2.9084</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6403</v>
+        <v>1.2531</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3572</v>
+        <v>0.5512</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2831</v>
+        <v>0.7019</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3964</v>
+        <v>2.1805</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3787</v>
+        <v>2.1805</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.139</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3706</v>
+        <v>-0.3651</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7684</v>
+        <v>-0.213</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2666</v>
+        <v>-1.7403</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5615</v>
+        <v>1.4013</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3336</v>
+        <v>-2.6197</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8952</v>
+        <v>4.021</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8957</v>
+        <v>1.0519</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7145</v>
+        <v>0.8243</v>
       </c>
       <c r="I21" t="n">
-        <v>3.6103</v>
+        <v>0.2276</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6427</v>
+        <v>-0.0034</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.2657</v>
+        <v>0.471</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9084</v>
+        <v>-0.4744</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2531</v>
+        <v>1.0552</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5512</v>
+        <v>0.3533</v>
       </c>
       <c r="O21" t="n">
         <v>0.7019</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7744</v>
+        <v>0.6864</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.2972</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7981</v>
+        <v>0.9835</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.7403</v>
+        <v>-0.337</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERRERA</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5088</v>
+        <v>1.0053</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.7169</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5088</v>
+        <v>0.2885</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4075</v>
+        <v>1.1078</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2717</v>
+        <v>1.6835</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1358</v>
+        <v>-0.5757</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1.4105</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1.9976</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.5871</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4075</v>
+        <v>-0.3027</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2717</v>
+        <v>-0.3141</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1358</v>
+        <v>0.0114</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.7751</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.7751</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1013</v>
+        <v>-0.4634</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.6936</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1013</v>
+        <v>0.2302</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>J. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.434</v>
+        <v>0.3964</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3094</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1246</v>
+        <v>0.3964</v>
       </c>
       <c r="G23" t="n">
-        <v>1.1078</v>
+        <v>0.4075</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6835</v>
+        <v>0.2717</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5757</v>
+        <v>0.1358</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4105</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1.9976</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5871</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3027</v>
+        <v>0.4075</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3141</v>
+        <v>0.2717</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0114</v>
+        <v>0.1358</v>
       </c>
       <c r="P23" t="n">
-        <v>2.7751</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7751</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0348</v>
+        <v>-0.011</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1011</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0663</v>
+        <v>-0.011</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0534</v>
+        <v>0.0308</v>
       </c>
       <c r="E24" t="n">
         <v>-0.31</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2565</v>
+        <v>0.3408</v>
       </c>
       <c r="G24" t="n">
         <v>0.8191000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>0.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2779</v>
+        <v>-0.1937</v>
       </c>
       <c r="T24" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2155</v>
+        <v>-0.1313</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.472</v>
+        <v>-2.5282</v>
       </c>
       <c r="E25" t="n">
         <v>-3.4384</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9663</v>
+        <v>0.9102</v>
       </c>
       <c r="G25" t="n">
         <v>-1.0093</v>
@@ -2404,13 +2404,13 @@
         <v>2.1805</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8414</v>
+        <v>-0.8975</v>
       </c>
       <c r="T25" t="n">
         <v>-0.6753</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.166</v>
+        <v>-0.2222</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8107</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.96</v>
+        <v>-3.1121</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.293</v>
+        <v>-4.4968</v>
       </c>
       <c r="F26" t="n">
-        <v>1.333</v>
+        <v>1.3846</v>
       </c>
       <c r="G26" t="n">
         <v>-1.4442</v>
@@ -2482,13 +2482,13 @@
         <v>2.1805</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1699</v>
+        <v>-0.3221</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3706</v>
+        <v>-0.5743</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2007</v>
+        <v>0.2523</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5441</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>18.1177</v>
+        <v>19.4756</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.954699999999999</v>
+        <v>-1.955000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>20.0723</v>
+        <v>21.4305</v>
       </c>
       <c r="G27" t="n">
         <v>20.4649</v>
@@ -2536,7 +2536,7 @@
         <v>15.0532</v>
       </c>
       <c r="K27" t="n">
-        <v>3.199400000000001</v>
+        <v>3.199399999999999</v>
       </c>
       <c r="L27" t="n">
         <v>11.8537</v>
@@ -2551,7 +2551,7 @@
         <v>2.8875</v>
       </c>
       <c r="P27" t="n">
-        <v>7.9289</v>
+        <v>7.928900000000001</v>
       </c>
       <c r="Q27" t="n">
         <v>-13.8754</v>
@@ -2560,13 +2560,13 @@
         <v>21.8047</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.7076</v>
+        <v>-2.3494</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.128299999999999</v>
+        <v>-4.1282</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4207</v>
+        <v>1.7789</v>
       </c>
       <c r="V27" t="n">
         <v>-6.5688</v>
